--- a/project_masterdoc.xlsx
+++ b/project_masterdoc.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GOV_04</t>
+          <t>NPC_08</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Mercy Otis Warren</t>
+          <t>Jessica Clear-Water</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -934,28 +934,28 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>SCHOLAR</t>
+          <t>LEADER &amp; CHIEF</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>USA / Patriot</t>
+          <t>CA / Indigenous Allies</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CA - OT / Ottawa</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>The historian watching the revolution happen. Events where what's being recorded matters as much as what's being done. Abolitionist themes.</t>
+          <t>Canada's de facto leader. Events about sovereignty, land rights, and what an alliance with the Continental Republic actually means for her people. The pivot character of the Canadian arc.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Faction: Patriot. Leads Abolitionist League.</t>
+          <t>isLeader=true. Faction: Indigenous Allies. Level 3. Starts Tile 201 (Ottawa). CAN_CLEARWATER_01 arc. questComplete=true.</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GOV_01</t>
+          <t>NPC_09</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Patrick Henry</t>
+          <t>Mark Penoit</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -982,28 +982,28 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ORATOR</t>
+          <t>DEPUTY GOVERNOR</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>USA / Patriot</t>
+          <t>CA / French Habitants</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>CA - QB / Saint-Georges</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>The revolution's loudest voice — and most suspicious of the government it's building. Events where ideological purity collides with pragmatic necessity.</t>
+          <t>Jessica's counterweight — he thinks in fortifications where she thinks in futures. Events about the gap between alliance theory and battlefield reality. The man holding the eastern flank.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Faction: Patriot. MilMods: Visionary(all) / Champion of Sun(L2+) / Healer(L3). Leads Sons of Liberty.</t>
+          <t>isVicePresident=true (double milMod as army commander). Faction: French Habitants. Level 2. Starts Tile 99 (Saint-Georges). CAN_PENOIT_01 arc.</t>
         </is>
       </c>
     </row>
@@ -1015,43 +1015,43 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GOV_08</t>
+          <t>GOV_04</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Phillis Wheatley</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Her poetry is reaching British-held territories and stoking rebellion from within. Events about cultural power as a weapon — words that outlast cannon fire.</t>
+          <t>Mercy Otis Warren</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>HERALD</t>
+          <t>SCHOLAR</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>USA / Abolitionist League</t>
+          <t>USA / Patriot</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>MA / Metro</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Eloquent / principled / transcendent / overlooked</t>
+          <t>The historian watching the revolution happen. Events where what's being recorded matters as much as what's being done. Abolitionist themes.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>ADDED</t>
+          <t>Faction: Patriot. Leads Abolitionist League.</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GOV_03</t>
+          <t>GOV_01</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Thomas Paine</t>
+          <t>Patrick Henry</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1078,28 +1078,28 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>SCHOLAR</t>
+          <t>ORATOR</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>USA / Radical</t>
+          <t>USA / Patriot</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>PA (immigrant)</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>The man who lit the fire with a pamphlet. Events where principles collide with governance — he trusts the people absolutely and is sometimes wrong.</t>
+          <t>The revolution's loudest voice — and most suspicious of the government it's building. Events where ideological purity collides with pragmatic necessity.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Faction: Radical. Leads Free Workers Union.</t>
+          <t>Faction: Patriot. MilMods: Visionary(all) / Champion of Sun(L2+) / Healer(L3). Leads Sons of Liberty.</t>
         </is>
       </c>
     </row>
@@ -1111,139 +1111,139 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GOV_06</t>
+          <t>GOV_08</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Ualani Carlisle</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
+          <t>Phillis Wheatley</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Her poetry is reaching British-held territories and stoking rebellion from within. Events about cultural power as a weapon — words that outlast cannon fire.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>PRESIDENT &amp; COMMANDER</t>
+          <t>HERALD</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>USA / Federal</t>
+          <t>USA / Abolitionist League</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>MA / Metro</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Eloquent / principled / transcendent / overlooked</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ADDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GOVERNOR_NAMED</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GOV_03</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Thomas Paine</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>SCHOLAR</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>USA / Radical</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>PA (immigrant)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>The man who lit the fire with a pamphlet. Events where principles collide with governance — he trusts the people absolutely and is sometimes wrong.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Faction: Radical. Leads Free Workers Union.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GOVERNOR_NAMED</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>GOV_06</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Ualani Carlisle</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>PRESIDENT &amp; COMMANDER</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>USA / Federal</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>DC (HI origin)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>The player character. Events that put the presidency on the line — DC falls / morale collapses / impossible choices. 17 security detail objections unread.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Faction: Federal. Starts Tile 188 (DC). Level 3. Commands APF personally.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>FACTION_LEADER</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>NPC_04</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Calico Jack</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>PRIVATEER</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>BA / Nassau Pirates</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Bahamas</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>The document in the dramatic coat. Events about the alliance of convenience — Nassau fights British for profit first patriotism second and the Republic should not forget this distinction.</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Leads Nassau Pirates + Loyalist Refugees. Level 1. Alliance triggered by CL_182. Army: Nassau Raiders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>FACTION_LEADER</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>NPC_02</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>General Howe</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED (NAME ONLY)</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>FIELD COMMANDER</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>UK / Military Command</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>NY / MA</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>The general who hesitated at Brooklyn when he could have ended it. Events about military authority vs. political restraint — and what happens when hesitation has a cost.</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Leads Tory Merchants + Military Command. Level 2. Starts Tile 14. Needs fleshing for events.</t>
         </is>
       </c>
     </row>
@@ -1255,43 +1255,43 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>NPC_03</t>
+          <t>NPC_04</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Governor Carleton</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED (NAME ONLY)</t>
+          <t>Calico Jack</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>COLONIAL GOVERNOR</t>
+          <t>PRIVATEER</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>CA / French Habitants</t>
+          <t>BA / Nassau Pirates</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>QC / Montreal</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Canada's impossible position — colonial by law, revolutionary by proximity. Events about who Canada's loyalty actually belongs to.</t>
+          <t>The document in the dramatic coat. Events about the alliance of convenience — Nassau fights British for profit first patriotism second and the Republic should not forget this distinction.</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Leads French Habitants + British Settlers + Indigenous Allies. Level 1. Starts Tile 201.</t>
+          <t>Leads Nassau Pirates + Loyalist Refugees. Level 1. Alliance triggered by CL_182. Army: Nassau Raiders.</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>NPC_01</t>
+          <t>NPC_02</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Lord Cornwallis</t>
+          <t>General Howe</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1318,124 +1318,124 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>FIELD COMMANDER</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>UK / Crown Loyalists</t>
+          <t>UK / Military Command</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr">
         <is>
+          <t>NY / MA</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>The general who hesitated at Brooklyn when he could have ended it. Events about military authority vs. political restraint — and what happens when hesitation has a cost.</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Leads Tory Merchants + Military Command. Level 2. Starts Tile 14. Needs fleshing for events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>FACTION_LEADER</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>NPC_03</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Governor Carleton</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (NAME ONLY)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>COLONIAL GOVERNOR</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>CA / French Habitants</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>QC / Montreal</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Canada's impossible position — colonial by law, revolutionary by proximity. Events about who Canada's loyalty actually belongs to.</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Leads French Habitants + British Settlers + Indigenous Allies. Level 1. Starts Tile 201.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>FACTION_LEADER</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>NPC_01</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Lord Cornwallis</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (NAME ONLY)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>UK / Crown Loyalists</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
           <t>VA / Carolinas</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>The man who surrendered Yorktown and can't forget it. Events that make him reluctant to repeat that mistake — or force him into exactly that position again.</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>Leads Crown Loyalists. Level 2. Starts Tile 14. Needs full governor.gd entry if used in UK-side events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>EVENT_NPC</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>NPC_07</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Anne Bonny</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>PRIVATEER</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>BA / Nassau Pirates</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Caribbean / Bahamas</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>She has a letter of marque and a grudge against the Royal Navy. Will raid British supply lines for the right price — but she operates on her own terms and her terms change.</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Historical pirate (game is already anachronistic). Nassau affiliate or independent. Naval combat events. Can be ally / mercenary / wild card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>EVENT_NPC</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NPC_06</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Joseph Brant (Thayendanegea)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Allied with the British because American expansion is the greater threat. Can be shown a different way — but only if the Republic can prove it means something different. Variable alignment event tree.</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>MOHAWK WAR CHIEF</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Indigenous / UK Ally</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>NY / Mohawk Valley</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Strategic / proud / pragmatic / betrayed by everyone</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
         </is>
       </c>
     </row>
@@ -1447,147 +1447,143 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
+          <t>NPC_07</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Anne Bonny</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>PRIVATEER</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>BA / Nassau Pirates</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Caribbean / Bahamas</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>She has a letter of marque and a grudge against the Royal Navy. Will raid British supply lines for the right price — but she operates on her own terms and her terms change.</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Historical pirate (game is already anachronistic). Nassau affiliate or independent. Naval combat events. Can be ally / mercenary / wild card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>EVENT_NPC</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>NPC_06</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Joseph Brant (Thayendanegea)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Allied with the British because American expansion is the greater threat. Can be shown a different way — but only if the Republic can prove it means something different. Variable alignment event tree.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>MOHAWK WAR CHIEF</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Indigenous / UK Ally</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>NY / Mohawk Valley</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Strategic / proud / pragmatic / betrayed by everyone</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>EVENT_NPC</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
           <t>NPC_05</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Patricia Eubanks</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>GETTYSBURG DOCENT</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>GEN</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Farmlands</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>She has narrated this field twice. Events where institutional memory — someone who just keeps showing up — becomes the emotional anchor of a moment.</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Featured in CL_006 / CX_005. 'Three days. Last time it was three days.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>PROTECTOR</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>PROT_03</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Bigfoot</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>STEALTH ASSET</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr"/>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Woods</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>Communicates through action rather than statement. Events where solidarity shows up as presence — vast and undeniable and officially denied. Eleven counties of footprints.</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>Summon event: PROT_03_SUMMON. Resource unlock: wood (25-40). Dev req: 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>PROTECTOR</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>PROT_06</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Chessie</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>NAVAL DETERRENT</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Wetlands</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Stirring the bay and bringing forth bounty. Events about what belongs to the water and what the water will protect. Three Royal Navy frigates reporting unexplained weather damage.</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Summon event: PROT_06_SUMMON. Resource unlock: food (30-50). Dev req: 2.</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1595,12 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PROT_16</t>
+          <t>PROT_03</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>Eternal Minuteman</t>
+          <t>Bigfoot</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1614,7 +1610,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>PERMANENT READINESS</t>
+          <t>STEALTH ASSET</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -1622,24 +1618,20 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+      <c r="G20" s="12" t="inlineStr"/>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Suburbs (Fixed Tile 61)</t>
+          <t>Woods</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>He was ready then. He is ready now. Events about what 'ready' means when the cause is permanent — the first shot still echoing / the same green at Lexington / the question whose answer is already known.</t>
+          <t>Communicates through action rather than statement. Events where solidarity shows up as presence — vast and undeniable and officially denied. Eleven counties of footprints.</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_16_SUMMON. Fixed tile 61. Resource unlock: manpower (30-50). Dev req: 3.</t>
+          <t>Summon event: PROT_03_SUMMON. Resource unlock: wood (25-40). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1643,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>PROT_13</t>
+          <t>PROT_06</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1666,7 +1658,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>SPECTRAL DEVELOPMENT</t>
+          <t>NAVAL DETERRENT</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1676,22 +1668,22 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Foothills</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>The Boys who never left. Events about place-loyalty — haunting as caretaking, presence as protection. Settlers working harder and not elaborating on why.</t>
+          <t>Stirring the bay and bringing forth bounty. Events about what belongs to the water and what the water will protect. Three Royal Navy frigates reporting unexplained weather damage.</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_13_SUMMON. Resource unlock: happiness (20-35). Dev req: 2.</t>
+          <t>Summon event: PROT_06_SUMMON. Resource unlock: food (30-50). Dev req: 2.</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1695,12 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PROT_05</t>
+          <t>PROT_16</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Headless Horseman</t>
+          <t>Eternal Minuteman</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1718,7 +1710,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>PSYCHOLOGICAL ASSET</t>
+          <t>PERMANENT READINESS</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -1728,22 +1720,22 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Woods</t>
+          <t>Suburbs (Fixed Tile 61)</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Cannot aim. Compensates with enthusiasm. Events where fear is the mission — Hudson Valley haunting runs / morale operations / British officers who decline to specify what they saw.</t>
+          <t>He was ready then. He is ready now. Events about what 'ready' means when the cause is permanent — the first shot still echoing / the same green at Lexington / the question whose answer is already known.</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_05_SUMMON. Resource unlock: dollars (25-40). Dev req: 4.</t>
+          <t>Summon event: PROT_16_SUMMON. Fixed tile 61. Resource unlock: manpower (30-50). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1747,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>PROT_02</t>
+          <t>PROT_13</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Jersey Devil</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1770,7 +1762,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>TERRITORIAL ASSET</t>
+          <t>SPECTRAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -1780,22 +1772,22 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Foothills</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Born under controversial circumstances in the Pine Barrens. Does not negotiate territory. Does not discuss his mother. Events about belonging to a place so completely it becomes defense.</t>
+          <t>The Boys who never left. Events about place-loyalty — haunting as caretaking, presence as protection. Settlers working harder and not elaborating on why.</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_02_SUMMON. Resource unlock: weapons (15-25). Dev req: 2.</t>
+          <t>Summon event: PROT_13_SUMMON. Resource unlock: happiness (20-35). Dev req: 2.</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1799,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PROT_12</t>
+          <t>PROT_05</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Headless Horseman</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1822,7 +1814,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>MORALE / MANDATE</t>
+          <t>PSYCHOLOGICAL ASSET</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -1832,22 +1824,22 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Metro (Fixed Tile 2)</t>
+          <t>Woods</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>The crack is a feature. Events about symbols and what they mean after they've broken — still ringing, still carrying, still the point.</t>
+          <t>Cannot aim. Compensates with enthusiasm. Events where fear is the mission — Hudson Valley haunting runs / morale operations / British officers who decline to specify what they saw.</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_12_SUMMON. Fixed tile 2. Resource unlock: dollars (30-50). Dev req: 4.</t>
+          <t>Summon event: PROT_05_SUMMON. Resource unlock: dollars (25-40). Dev req: 4.</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1851,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>PROT_17</t>
+          <t>PROT_02</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Lincoln's Ghost</t>
+          <t>Jersey Devil</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1874,7 +1866,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>EMANCIPATION / MANDATE</t>
+          <t>TERRITORIAL ASSET</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1884,22 +1876,22 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Metro (Fixed Tile 188)</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Still in the White House. Has opinions about the East Bedroom. Events where the weight of freedom's unfinished business arrives at 2am with something useful to say. The arc bends. This is the bending part.</t>
+          <t>Born under controversial circumstances in the Pine Barrens. Does not negotiate territory. Does not discuss his mother. Events about belonging to a place so completely it becomes defense.</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_17_SUMMON. Fixed tile 188. Resource unlock: mandate (20-35). Dev req: 3.</t>
+          <t>Summon event: PROT_02_SUMMON. Resource unlock: weapons (15-25). Dev req: 2.</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1903,12 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PROT_01</t>
+          <t>PROT_12</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Mothman</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1926,7 +1918,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>AERIAL SURVEYOR</t>
+          <t>MORALE / MANDATE</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -1936,22 +1928,22 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>WV</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Foothills</t>
+          <t>Metro (Fixed Tile 2)</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Has been trying to warn people for decades. Nobody listened until now. Events where intelligence comes from impossible sources — and what do you do when the warning is real.</t>
+          <t>The crack is a feature. Events about symbols and what they mean after they've broken — still ringing, still carrying, still the point.</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_01_SUMMON. Content flag: kinky_lewd. Resource unlock: food (20-35). Dev req: 3.</t>
+          <t>Summon event: PROT_12_SUMMON. Fixed tile 2. Resource unlock: dollars (30-50). Dev req: 4.</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1955,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>PROT_14</t>
+          <t>PROT_17</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Lincoln's Ghost</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1978,7 +1970,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>MANIFEST ECONOMY</t>
+          <t>EMANCIPATION / MANDATE</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -1986,20 +1978,24 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Metro (Fixed Tile 188)</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Four presidents in the situation room. Events where history and present collide — Roosevelt interrupting / Jefferson raising philosophical objections / Lincoln quietly approving of Carlisle.</t>
+          <t>Still in the White House. Has opinions about the East Bedroom. Events where the weight of freedom's unfinished business arrives at 2am with something useful to say. The arc bends. This is the bending part.</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_14_SUMMON. Content flag: kinky_lewd. Resource unlock: mandate (25-40). Dev req: 5.</t>
+          <t>Summon event: PROT_17_SUMMON. Fixed tile 188. Resource unlock: mandate (20-35). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2007,12 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PROT_08</t>
+          <t>PROT_01</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Mothman</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2026,7 +2022,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>NAVAL SUPERIORITY</t>
+          <t>AERIAL SURVEYOR</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2036,22 +2032,22 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>WV</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Wetlands (Fixed Tile 63)</t>
+          <t>Foothills</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>The ship that cannot die. Events about legacy and refusal — things that are too important to let go even when the official order comes down. Three admirals tried.</t>
+          <t>Has been trying to warn people for decades. Nobody listened until now. Events where intelligence comes from impossible sources — and what do you do when the warning is real.</t>
         </is>
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_08_SUMMON. Fixed tile 63. Resource unlock: weapons (30-50). Dev req: 5.</t>
+          <t>Summon event: PROT_01_SUMMON. Content flag: kinky_lewd. Resource unlock: food (20-35). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2059,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>PROT_11</t>
+          <t>PROT_14</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2078,7 +2074,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>RAPID MOBILIZATION</t>
+          <t>MANIFEST ECONOMY</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -2086,24 +2082,20 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+      <c r="G29" s="12" t="inlineStr"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Suburbs</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>He has done this before and he will do it again with the same energy as the first time. Events about urgency — the moment when the warning has to reach everyone and there is exactly one ride to do it.</t>
+          <t>Four presidents in the situation room. Events where history and present collide — Roosevelt interrupting / Jefferson raising philosophical objections / Lincoln quietly approving of Carlisle.</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_11_SUMMON. Resource unlock: culture (20-35). Dev req: 3.</t>
+          <t>Summon event: PROT_14_SUMMON. Content flag: kinky_lewd. Resource unlock: mandate (25-40). Dev req: 5.</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2107,12 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PROT_15</t>
+          <t>PROT_08</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Skunk Ape</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>WETLAND ENFORCEMENT</t>
+          <t>NAVAL SUPERIORITY</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2140,22 +2132,22 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Wetlands (Fixed Tile 63)</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>He has been here longer than the settlers. Events about Florida — which has always operated by different rules — and what it means that even the swamp takes sides.</t>
+          <t>The ship that cannot die. Events about legacy and refusal — things that are too important to let go even when the official order comes down. Three admirals tried.</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_15_SUMMON. Resource unlock: food (15-25). Dev req: 2.</t>
+          <t>Summon event: PROT_08_SUMMON. Fixed tile 63. Resource unlock: weapons (30-50). Dev req: 5.</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2159,12 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>PROT_10</t>
+          <t>PROT_11</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2182,7 +2174,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>TERRITORIAL ASSET</t>
+          <t>RAPID MOBILIZATION</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -2192,22 +2184,22 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Foothills</t>
+          <t>Suburbs</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Bridges Old World fears and New World land. Events about settlers and what they carried with them — and what the mountains had here long before anyone carried anything.</t>
+          <t>He has done this before and he will do it again with the same energy as the first time. Events about urgency — the moment when the warning has to reach everyone and there is exactly one ride to do it.</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_10_SUMMON. Resource unlock: metal (15-25). Dev req: 3.</t>
+          <t>Summon event: PROT_11_SUMMON. Resource unlock: culture (20-35). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2211,12 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PROT_07</t>
+          <t>PROT_15</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>The Bell Witch</t>
+          <t>Skunk Ape</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>PSYCHOLOGICAL WARFARE</t>
+          <t>WETLAND ENFORCEMENT</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2244,22 +2236,22 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Foothills</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Operates on her own terms. Does not follow orders — only alignment of interests. Events where psychological pressure becomes military advantage. Andrew Jackson will not return to that farmhouse.</t>
+          <t>He has been here longer than the settlers. Events about Florida — which has always operated by different rules — and what it means that even the swamp takes sides.</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_07_SUMMON. Resource unlock: magic (10-20). Dev req: 3.</t>
+          <t>Summon event: PROT_15_SUMMON. Resource unlock: food (15-25). Dev req: 2.</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2263,12 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>PROT_04</t>
+          <t>PROT_10</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2286,7 +2278,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>WEATHER ASSET</t>
+          <t>TERRITORIAL ASSET</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -2296,22 +2288,22 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Woods</t>
+          <t>Foothills</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Indigenous skies reclaiming themselves. Events where the revolution aligns with older grievances — the storm does not fight for the Republic so much as against the same enemy.</t>
+          <t>Bridges Old World fears and New World land. Events about settlers and what they carried with them — and what the mountains had here long before anyone carried anything.</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>Summon event: PROT_04_SUMMON. Resource unlock: culture (20-35). Dev req: 3.</t>
+          <t>Summon event: PROT_10_SUMMON. Resource unlock: metal (15-25). Dev req: 3.</t>
         </is>
       </c>
     </row>
@@ -2323,151 +2315,151 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
+          <t>PROT_07</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>The Bell Witch</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>PSYCHOLOGICAL WARFARE</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Foothills</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>Operates on her own terms. Does not follow orders — only alignment of interests. Events where psychological pressure becomes military advantage. Andrew Jackson will not return to that farmhouse.</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Summon event: PROT_07_SUMMON. Resource unlock: magic (10-20). Dev req: 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>PROTECTOR</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>PROT_04</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Thunderbird</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>WEATHER ASSET</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>Woods</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Indigenous skies reclaiming themselves. Events where the revolution aligns with older grievances — the storm does not fight for the Republic so much as against the same enemy.</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Summon event: PROT_04_SUMMON. Resource unlock: culture (20-35). Dev req: 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>PROTECTOR</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
           <t>PROT_09</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Valley Forge Guardian</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>WINTER RESILIENCE</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="H34" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>Fortress (Fixed Tile 1)</t>
         </is>
       </c>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>Not Washington — the army itself. Events about what endurance means when there is nothing left but staying. The ground that remembers starving and still holds the line.</t>
         </is>
       </c>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>Summon event: PROT_09_SUMMON. Fixed tile 1. Resource unlock: manpower (50-80). Dev req: 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>ARCHETYPE</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>ARC_22</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Acadian Forest Ranger</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>SCOUT</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>VT/NH/ME/Canada border</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>Woods|Wetlands</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>The Acadians were displaced twice. Events: borderland intelligence / Canada alliance complexities / French-speaking America.</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>Army: Forest Rangers. Pool: NP_06 (French/Acadian).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>ARCHETYPE</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>ARC_02</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Appalachian Miner</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>ENGINEER</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>WV/PA/VA</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>Foothills</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>The mountain knows what armies don't. Events: tunnel warfare / resource extraction under fire / Crown mining operations.</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>Army: Mountain Militia. Name pool: NP_03 (Southern Appalachian).</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2471,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>ARC_21</t>
+          <t>ARC_22</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Border Mercenary</t>
+          <t>Acadian Forest Ranger</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2494,7 +2486,7 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>SCOUT</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
@@ -2504,22 +2496,22 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>Any Border</t>
+          <t>VT/NH/ME/Canada border</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Suburbs|Farmlands</t>
+          <t>Woods|Wetlands</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>Fights for whoever pays. Has been paid by the Republic. Events: mercenary loyalty tests / the moment money isn't enough / defection risk.</t>
+          <t>The Acadians were displaced twice. Events: borderland intelligence / Canada alliance complexities / French-speaking America.</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>Army: Border Company. Pools: NP_03 / NP_05.</t>
+          <t>Army: Forest Rangers. Pool: NP_06 (French/Acadian).</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2523,12 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>ARC_11</t>
+          <t>ARC_02</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Boston Rabble-Rouser</t>
+          <t>Appalachian Miner</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2546,7 +2538,7 @@
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>ORATOR</t>
+          <t>ENGINEER</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -2556,22 +2548,22 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>MA / Boston</t>
+          <t>WV/PA/VA</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Foothills</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>The voice that turns a crowd into a movement. Events: propaganda / faction loyalty swings / tea parties (metaphorical and otherwise).</t>
+          <t>The mountain knows what armies don't. Events: tunnel warfare / resource extraction under fire / Crown mining operations.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>Army: Sons of Liberty. Pools: NP_01 / NP_09.</t>
+          <t>Army: Mountain Militia. Name pool: NP_03 (Southern Appalachian).</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2575,12 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>ARC_19</t>
+          <t>ARC_21</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Caribbean Privateer</t>
+          <t>Border Mercenary</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2598,7 +2590,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>ADMIRAL</t>
+          <t>SOLDIER</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -2608,22 +2600,22 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>Caribbean / Any Port</t>
+          <t>Any Border</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Wetlands|Suburbs</t>
+          <t>Suburbs|Farmlands</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>Fighting for profit that happens to align with the cause. Events: Nassau alliance support / privateering contracts / the difference between a pirate and a patriot.</t>
+          <t>Fights for whoever pays. Has been paid by the Republic. Events: mercenary loyalty tests / the moment money isn't enough / defection risk.</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>Army: Privateer Corps. Pool: NP_05. Calico Jack / Anne Bonny story hooks.</t>
+          <t>Army: Border Company. Pools: NP_03 / NP_05.</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2627,12 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>ARC_25</t>
+          <t>ARC_11</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Carnival Barker</t>
+          <t>Boston Rabble-Rouser</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2660,22 +2652,22 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>Any Port/Swamp</t>
+          <t>MA / Boston</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Wetlands|Suburbs</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>The propagandist you didn't hire but got anyway. Events: information warfare / morale manipulation / the spectacular stunt that somehow works.</t>
+          <t>The voice that turns a crowd into a movement. Events: propaganda / faction loyalty swings / tea parties (metaphorical and otherwise).</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>Army: Showmen's Rifles. Pools: NP_03 / NP_05.</t>
+          <t>Army: Sons of Liberty. Pools: NP_01 / NP_09.</t>
         </is>
       </c>
     </row>
@@ -2687,12 +2679,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>ARC_06</t>
+          <t>ARC_19</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Chesapeake Shipwright</t>
+          <t>Caribbean Privateer</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2702,7 +2694,7 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>ENGINEER</t>
+          <t>ADMIRAL</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
@@ -2712,22 +2704,22 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>MD/VA/DE</t>
+          <t>Caribbean / Any Port</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Wetlands|Suburbs</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>Builds the boats that win naval engagements. Events: harbor defense / supply routes / what happens when the bay takes sides (see Chessie).</t>
+          <t>Fighting for profit that happens to align with the cause. Events: Nassau alliance support / privateering contracts / the difference between a pirate and a patriot.</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>Army: Harbor Guard. Pools: NP_01 / NP_04.</t>
+          <t>Army: Privateer Corps. Pool: NP_05. Calico Jack / Anne Bonny story hooks.</t>
         </is>
       </c>
     </row>
@@ -2739,12 +2731,12 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>ARC_12</t>
+          <t>ARC_25</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Continental Surgeon</t>
+          <t>Carnival Barker</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2754,7 +2746,7 @@
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>HEALER</t>
+          <t>ORATOR</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -2764,22 +2756,22 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>PA/VA/NY</t>
+          <t>Any Port/Swamp</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Farmlands|Foothills</t>
+          <t>Wetlands|Suburbs</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>Has seen everything. Events: field medicine under fire / the moral weight of triage / what surgeons know about war that generals don't.</t>
+          <t>The propagandist you didn't hire but got anyway. Events: information warfare / morale manipulation / the spectacular stunt that somehow works.</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>Army: Continental Corps. Pools: NP_01 / NP_02.</t>
+          <t>Army: Showmen's Rifles. Pools: NP_03 / NP_05.</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2783,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>ARC_15</t>
+          <t>ARC_06</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>DC Bureaucrat</t>
+          <t>Chesapeake Shipwright</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2806,7 +2798,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>BUREAUCRAT</t>
+          <t>ENGINEER</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -2816,22 +2808,22 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>DC / Any Metro</t>
+          <t>MD/VA/DE</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>Keeps the Republic running while everyone else is fighting. Events: mandate/corruption crises / the infrastructure of revolution / 'the paperwork has to be filed.'</t>
+          <t>Builds the boats that win naval engagements. Events: harbor defense / supply routes / what happens when the bay takes sides (see Chessie).</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Army: Federal Guard. Pools: NP_01 / NP_04.</t>
+          <t>Army: Harbor Guard. Pools: NP_01 / NP_04.</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2835,12 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>ARC_14</t>
+          <t>ARC_12</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Frontier Preacher</t>
+          <t>Continental Surgeon</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2858,7 +2850,7 @@
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>ORATOR</t>
+          <t>HEALER</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -2868,22 +2860,22 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>VA/WV/TN/KY</t>
+          <t>PA/VA/NY</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Woods|Foothills</t>
+          <t>Farmlands|Foothills</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>The sermon that reaches places armies can't. Events: faith organizing / frontier settlement / the preacher who shows up during the occupation and keeps going.</t>
+          <t>Has seen everything. Events: field medicine under fire / the moral weight of triage / what surgeons know about war that generals don't.</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>Army: Righteous Rifles. Pool: NP_03. Pairs with Francis Asbury event arcs.</t>
+          <t>Army: Continental Corps. Pools: NP_01 / NP_02.</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2887,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>ARC_23</t>
+          <t>ARC_15</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>Gettysburg Descendant</t>
+          <t>DC Bureaucrat</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2910,7 +2902,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>BUREAUCRAT</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
@@ -2920,22 +2912,22 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>PA/MD</t>
+          <t>DC / Any Metro</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Farmlands|Foothills</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>Carries the weight of what happened here before. Events: Gettysburg significance / Patricia Eubanks crossover / the second time this field matters.</t>
+          <t>Keeps the Republic running while everyone else is fighting. Events: mandate/corruption crises / the infrastructure of revolution / 'the paperwork has to be filed.'</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Army: Heritage Guard. Pools: NP_01 / NP_04.</t>
+          <t>Army: Federal Guard. Pools: NP_01 / NP_04.</t>
         </is>
       </c>
     </row>
@@ -2947,12 +2939,12 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>ARC_05</t>
+          <t>ARC_14</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Green Mountain Farmer</t>
+          <t>Frontier Preacher</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2962,7 +2954,7 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>FARMER</t>
+          <t>ORATOR</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -2972,22 +2964,22 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>VT/NH</t>
+          <t>VA/WV/TN/KY</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Foothills|Farmlands</t>
+          <t>Woods|Foothills</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Vermont energy. Events: community defense / food security under occupation / the farmer who showed up with a musket and stayed.</t>
+          <t>The sermon that reaches places armies can't. Events: faith organizing / frontier settlement / the preacher who shows up during the occupation and keeps going.</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>Army: Green Mountain Boys. Pools: NP_01 / NP_06 (French/Acadian).</t>
+          <t>Army: Righteous Rifles. Pool: NP_03. Pairs with Francis Asbury event arcs.</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2991,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>ARC_20</t>
+          <t>ARC_23</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Hawaiian Refugee</t>
+          <t>Gettysburg Descendant</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -3014,7 +3006,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>SOLDIER</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -3024,22 +3016,22 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>HI / Any Metro</t>
+          <t>PA/MD</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Wetlands|Metro</t>
+          <t>Farmlands|Foothills</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>Far from home in a war that's also theirs. Events: Pacific connection / diplomatic bridge / being the one person who understands both worlds.</t>
+          <t>Carries the weight of what happened here before. Events: Gettysburg significance / Patricia Eubanks crossover / the second time this field matters.</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Army: Pacific Guard. Pool: NP_08 (Hawaiian). Thematic pair with Ualani Carlisle.</t>
+          <t>Army: Heritage Guard. Pools: NP_01 / NP_04.</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3043,12 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>ARC_10</t>
+          <t>ARC_05</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Indigenous Scout</t>
+          <t>Green Mountain Farmer</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -3066,7 +3058,7 @@
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>SCOUT</t>
+          <t>FARMER</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -3076,22 +3068,22 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>Any Woods/Wetlands</t>
+          <t>VT/NH</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Woods|Wetlands</t>
+          <t>Foothills|Farmlands</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>Navigates territory as a native — which means knowing things armies can't know. Events: indigenous alliance tensions / land promises / what the Republic will and won't guarantee.</t>
+          <t>Vermont energy. Events: community defense / food security under occupation / the farmer who showed up with a musket and stayed.</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Army: Ranger Company. Pool: NP_07.</t>
+          <t>Army: Green Mountain Boys. Pools: NP_01 / NP_06 (French/Acadian).</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3095,12 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>ARC_03</t>
+          <t>ARC_20</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Ivy League Dropout</t>
+          <t>Hawaiian Refugee</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -3118,7 +3110,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>SCHOLAR</t>
+          <t>DIPLOMAT</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
@@ -3128,22 +3120,22 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>Boston/Philadelphia/NYC</t>
+          <t>HI / Any Metro</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Wetlands|Metro</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>Left the academy for the cause. Events: intelligence work / propaganda / the tension between education and action.</t>
+          <t>Far from home in a war that's also theirs. Events: Pacific connection / diplomatic bridge / being the one person who understands both worlds.</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Army: Volunteer Regiment. Pools: NP_01 / NP_09 (Irish) / NP_10 (Jewish).</t>
+          <t>Army: Pacific Guard. Pool: NP_08 (Hawaiian). Thematic pair with Ualani Carlisle.</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3147,12 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>ARC_24</t>
+          <t>ARC_10</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>LGBTQ+ Organizer</t>
+          <t>Indigenous Scout</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>SCOUT</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -3180,22 +3172,22 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>Any Metro/Suburb</t>
+          <t>Any Woods/Wetlands</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Metro|Suburbs</t>
+          <t>Woods|Wetlands</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>Organizing the revolution within the revolution. Events: mandate and harmony / community defense / what freedom means when it means everyone.</t>
+          <t>Navigates territory as a native — which means knowing things armies can't know. Events: indigenous alliance tensions / land promises / what the Republic will and won't guarantee.</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>Army: Solidarity Regiment. Pools: NP_01 / NP_04 / NP_09.</t>
+          <t>Army: Ranger Company. Pool: NP_07.</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3199,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>ARC_07</t>
+          <t>ARC_03</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Loyalist Turncoat</t>
+          <t>Ivy League Dropout</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3222,7 +3214,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SCHOLAR</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
@@ -3232,22 +3224,22 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>NY/PA</t>
+          <t>Boston/Philadelphia/NYC</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>Metro|Suburbs</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>Someone who switched sides and carries the weight of what they did before. Events: double-agent dynamics / loyalty tests / the moment of choosing. Perfect Codebook commander.</t>
+          <t>Left the academy for the cause. Events: intelligence work / propaganda / the tension between education and action.</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Army: Irregular Rifles. Pools: NP_01 / NP_02 (German).</t>
+          <t>Army: Volunteer Regiment. Pools: NP_01 / NP_09 (Irish) / NP_10 (Jewish).</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3251,12 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>ARC_13</t>
+          <t>ARC_24</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Nantucket Sailor</t>
+          <t>LGBTQ+ Organizer</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3274,7 +3266,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>ADMIRAL</t>
+          <t>DIPLOMAT</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -3284,22 +3276,22 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>MA / Nantucket</t>
+          <t>Any Metro/Suburb</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Metro|Suburbs</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>The water is their home. Events: naval engagements / whale-road intelligence / Old Ironsides crew candidates.</t>
+          <t>Organizing the revolution within the revolution. Events: mandate and harmony / community defense / what freedom means when it means everyone.</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>Army: Naval Infantry. Pool: NP_01.</t>
+          <t>Army: Solidarity Regiment. Pools: NP_01 / NP_04 / NP_09.</t>
         </is>
       </c>
     </row>
@@ -3311,12 +3303,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>ARC_17</t>
+          <t>ARC_07</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Plantation Deserter</t>
+          <t>Loyalist Turncoat</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3326,7 +3318,7 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>SOLDIER</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -3336,22 +3328,22 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>VA/NC/SC/GA</t>
+          <t>NY/PA</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>Farmlands</t>
+          <t>Metro|Suburbs</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>Left. Won't return. Events: freedom-seeking narrative / what the revolution owes / the soldier who is fighting for something different than everyone else.</t>
+          <t>Someone who switched sides and carries the weight of what they did before. Events: double-agent dynamics / loyalty tests / the moment of choosing. Perfect Codebook commander.</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Army: Freedom Rifles. Pool: NP_04.</t>
+          <t>Army: Irregular Rifles. Pools: NP_01 / NP_02 (German).</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3355,12 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>ARC_16</t>
+          <t>ARC_13</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Rust Belt Steelworker</t>
+          <t>Nantucket Sailor</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3378,7 +3370,7 @@
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>ENGINEER</t>
+          <t>ADMIRAL</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -3388,22 +3380,22 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>PA/OH/NJ</t>
+          <t>MA / Nantucket</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Suburbs</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>The worker who built the weapons. Events: production under occupation / sabotage from inside the factory / labor organization.</t>
+          <t>The water is their home. Events: naval engagements / whale-road intelligence / Old Ironsides crew candidates.</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>Army: Iron Brigade. Pools: NP_02 / NP_09.</t>
+          <t>Army: Naval Infantry. Pool: NP_01.</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3407,12 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>ARC_04</t>
+          <t>ARC_17</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Seminole Fighter</t>
+          <t>Plantation Deserter</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -3430,7 +3422,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>WARRIOR</t>
+          <t>SOLDIER</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
@@ -3440,22 +3432,22 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>FL/SC/GA</t>
+          <t>VA/NC/SC/GA</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>Wetlands|Farmlands</t>
+          <t>Farmlands</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>The revolution within the revolution. Events: Indigenous-colonial alliance tensions / Florida territory / the war this person has already been fighting.</t>
+          <t>Left. Won't return. Events: freedom-seeking narrative / what the revolution owes / the soldier who is fighting for something different than everyone else.</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>Army: Forest Skirmishers. Pool: NP_07 (Indigenous).</t>
+          <t>Army: Freedom Rifles. Pool: NP_04.</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3459,12 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>ARC_18</t>
+          <t>ARC_16</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Swamp Witch</t>
+          <t>Rust Belt Steelworker</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3482,7 +3474,7 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>MAGE</t>
+          <t>ENGINEER</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -3492,22 +3484,22 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>LA/FL/SC/GA</t>
+          <t>PA/OH/NJ</t>
         </is>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Wetlands</t>
+          <t>Suburbs</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>Not a soldier. Something else. Events: folk magic / bayou knowledge / the supernatural undercurrent beneath colonial America. The Bell Witch's neighbor.</t>
+          <t>The worker who built the weapons. Events: production under occupation / sabotage from inside the factory / labor organization.</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>Army: Bayou Raiders. Pools: NP_04 / NP_05 (Spanish/Caribbean).</t>
+          <t>Army: Iron Brigade. Pools: NP_02 / NP_09.</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3511,12 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>ARC_08</t>
+          <t>ARC_04</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Tobacco Belt Drifter</t>
+          <t>Seminole Fighter</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3534,7 +3526,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>SCOUT</t>
+          <t>WARRIOR</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
@@ -3544,22 +3536,22 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>VA/NC/SC/GA</t>
+          <t>FL/SC/GA</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>Farmlands</t>
+          <t>Wetlands|Farmlands</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>Intel from plantation country. Events: supply route sabotage / plantation economy / freedom-seeking enslaved persons they've encountered on the road.</t>
+          <t>The revolution within the revolution. Events: Indigenous-colonial alliance tensions / Florida territory / the war this person has already been fighting.</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
         <is>
-          <t>Army: Frontier Militia. Pools: NP_03 / NP_04.</t>
+          <t>Army: Forest Skirmishers. Pool: NP_07 (Indigenous).</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3563,12 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>ARC_09</t>
+          <t>ARC_18</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>War Widow</t>
+          <t>Swamp Witch</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3586,7 +3578,7 @@
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>DIPLOMAT</t>
+          <t>MAGE</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -3596,22 +3588,22 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Any Suburb/Metro</t>
+          <t>LA/FL/SC/GA</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Suburbs|Metro</t>
+          <t>Wetlands</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>Lost someone and turned it into fuel. Events: civilian resistance / community organizing / the cost of the revolution measured in who isn't here anymore.</t>
+          <t>Not a soldier. Something else. Events: folk magic / bayou knowledge / the supernatural undercurrent beneath colonial America. The Bell Witch's neighbor.</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>Army: Liberty Brigade. Pools: NP_01 / NP_04 / NP_09.</t>
+          <t>Army: Bayou Raiders. Pools: NP_04 / NP_05 (Spanish/Caribbean).</t>
         </is>
       </c>
     </row>
@@ -3623,45 +3615,149 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
+          <t>ARC_08</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Tobacco Belt Drifter</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>SCOUT</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>VA/NC/SC/GA</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>Farmlands</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>Intel from plantation country. Events: supply route sabotage / plantation economy / freedom-seeking enslaved persons they've encountered on the road.</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>Army: Frontier Militia. Pools: NP_03 / NP_04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>ARCHETYPE</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>ARC_09</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>War Widow</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>DIPLOMAT</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>Any Suburb/Metro</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>Suburbs|Metro</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>Lost someone and turned it into fuel. Events: civilian resistance / community organizing / the cost of the revolution measured in who isn't here anymore.</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>Army: Liberty Brigade. Pools: NP_01 / NP_04 / NP_09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>ARCHETYPE</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
           <t>ARC_01</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>Wetlands Fisher</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>SCOUT</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F61" s="14" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>WV/NJ/MD/SC</t>
         </is>
       </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>Wetlands</t>
         </is>
       </c>
-      <c r="I59" s="14" t="inlineStr">
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>Guerrilla intel from the marshes. Events: local knowledge beats military strategy.</t>
         </is>
       </c>
-      <c r="J59" s="14" t="inlineStr">
+      <c r="J61" s="14" t="inlineStr">
         <is>
           <t>Army: Wetlands Rangers. Name pools: NP_01 (English) / NP_04 (African American).</t>
         </is>
@@ -4926,7 +5022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5372,101 +5468,101 @@
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>GOVERNOR_NAMED</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>NPC_08</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Jessica Clear-Water</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>GOVERNOR_NAMED</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>NPC_09</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Mark Penoit</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>FACTION_LEADER</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>NPC_04</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Calico Jack</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>IMPLEMENTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>EVENT_NPC</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>NPC_05</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Patricia Eubanks</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>EVENT_NPC</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NPC_06</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Joseph Brant (Thayendanegea)</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>Allied with the British because American expansion is the greater threat. Can be shown a different way — but only if the Republic can prove it means something different. Variable alignment event tree.</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5574,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>NPC_07</t>
+          <t>NPC_05</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Anne Bonny</t>
+          <t>Patricia Eubanks</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
@@ -5499,73 +5595,73 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>EVENT_NPC</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>NPC_06</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Joseph Brant (Thayendanegea)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Allied with the British because American expansion is the greater threat. Can be shown a different way — but only if the Republic can prove it means something different. Variable alignment event tree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>EVENT_NPC</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>NPC_07</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Anne Bonny</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
           <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>PROTECTOR</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>PROT_01</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Mothman</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>PROTECTOR</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>PROT_02</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Jersey Devil</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED</t>
         </is>
       </c>
     </row>
@@ -5577,18 +5673,18 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PROT_03</t>
+          <t>PROT_01</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>Bigfoot</t>
+          <t>Mothman</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -5610,12 +5706,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>PROT_04</t>
+          <t>PROT_02</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Thunderbird</t>
+          <t>Jersey Devil</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -5643,12 +5739,12 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PROT_05</t>
+          <t>PROT_03</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Headless Horseman</t>
+          <t>Bigfoot</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
@@ -5676,12 +5772,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>PROT_06</t>
+          <t>PROT_04</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>Chessie</t>
+          <t>Thunderbird</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -5709,12 +5805,12 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PROT_07</t>
+          <t>PROT_05</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>The Bell Witch</t>
+          <t>Headless Horseman</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
@@ -5742,12 +5838,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>PROT_08</t>
+          <t>PROT_06</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Old Ironsides</t>
+          <t>Chessie</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
@@ -5775,12 +5871,12 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PROT_09</t>
+          <t>PROT_07</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Valley Forge Guardian</t>
+          <t>The Bell Witch</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr"/>
@@ -5808,12 +5904,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>PROT_10</t>
+          <t>PROT_08</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Snallygaster</t>
+          <t>Old Ironsides</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
@@ -5841,12 +5937,12 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PROT_11</t>
+          <t>PROT_09</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Paul Revere</t>
+          <t>Valley Forge Guardian</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr"/>
@@ -5874,12 +5970,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>PROT_12</t>
+          <t>PROT_10</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Liberty Bell</t>
+          <t>Snallygaster</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -5907,12 +6003,12 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PROT_13</t>
+          <t>PROT_11</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Green Mountain Ghost</t>
+          <t>Paul Revere</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr"/>
@@ -5940,18 +6036,18 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>PROT_14</t>
+          <t>PROT_12</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Mount Rushmore</t>
+          <t>Liberty Bell</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -5973,12 +6069,12 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PROT_15</t>
+          <t>PROT_13</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Skunk Ape</t>
+          <t>Green Mountain Ghost</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr"/>
@@ -6006,18 +6102,18 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>PROT_16</t>
+          <t>PROT_14</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Eternal Minuteman</t>
+          <t>Mount Rushmore</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -6039,12 +6135,12 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PROT_17</t>
+          <t>PROT_15</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>Lincoln's Ghost</t>
+          <t>Skunk Ape</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr"/>
@@ -6065,27 +6161,23 @@
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>DE_001</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>A NEW WAR FOR AN OLD REPUBLIC</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>president_address</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>PROTECTOR</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>PROT_16</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Eternal Minuteman</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6095,30 +6187,30 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>DE_002</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>HAPPY NEW YEAR: Redcoats Ring in Revolution</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>fireworks_muskets</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>PROTECTOR</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>PROT_17</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Lincoln's Ghost</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr"/>
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -6128,7 +6220,11 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr"/>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -6138,17 +6234,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>DE_003</t>
+          <t>DE_001</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>LOVE IN A TIME OF MUSKETS</t>
+          <t>A NEW WAR FOR AN OLD REPUBLIC</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>heart_cannon</t>
+          <t>president_address</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -6171,17 +6267,17 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>DE_004</t>
+          <t>DE_002</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>INDEPENDENCE DAY: We Did It Once We're Doing It Again</t>
+          <t>HAPPY NEW YEAR: Redcoats Ring in Revolution</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>fourth_of_july</t>
+          <t>fireworks_muskets</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
@@ -6204,17 +6300,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>DE_005</t>
+          <t>DE_003</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>HALLOWS' EVE: Mothman Spotted Over West Virginia</t>
+          <t>LOVE IN A TIME OF MUSKETS</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>mothman_silhouette</t>
+          <t>heart_cannon</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -6237,17 +6333,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>CL_182</t>
+          <t>DE_004</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>NASSAU FALLS: THE PIRATES STAND WITH THE REPUBLIC</t>
+          <t>INDEPENDENCE DAY: We Did It Once We're Doing It Again</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>nassau_alliance</t>
+          <t>fourth_of_july</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
@@ -6270,17 +6366,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>CL_001</t>
+          <t>DE_005</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>NYC FALLS TO THE REPUBLIC</t>
+          <t>HALLOWS' EVE: Mothman Spotted Over West Virginia</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>nyc_liberation</t>
+          <t>mothman_silhouette</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -6303,17 +6399,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>CL_006</t>
+          <t>CL_182</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>GETTYSBURG SECURED</t>
+          <t>NASSAU FALLS: THE PIRATES STAND WITH THE REPUBLIC</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>gettysburg_memorial</t>
+          <t>nassau_alliance</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
@@ -6336,17 +6432,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>CL_007</t>
+          <t>CL_001</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>KENNETT SQUARE FREE</t>
+          <t>NYC FALLS TO THE REPUBLIC</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>mushroom_victory</t>
+          <t>nyc_liberation</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -6369,17 +6465,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>CL_009</t>
+          <t>CL_006</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>BRATTLEBORO LIBERATED</t>
+          <t>GETTYSBURG SECURED</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>brattleboro_liberation</t>
+          <t>gettysburg_memorial</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -6402,17 +6498,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>CX_001</t>
+          <t>CL_007</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>DC FALLS: Government in Temporary Relocation</t>
+          <t>KENNETT SQUARE FREE</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>dc_falls</t>
+          <t>mushroom_victory</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -6435,17 +6531,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>CX_005</t>
+          <t>CL_009</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>GETTYSBURG TAKEN</t>
+          <t>BRATTLEBORO LIBERATED</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>gettysburg_lost</t>
+          <t>brattleboro_liberation</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -6468,17 +6564,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>SL_001</t>
+          <t>CX_001</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>PENNSYLVANIA FULLY LIBERATED</t>
+          <t>DC FALLS: Government in Temporary Relocation</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>pa_liberated</t>
+          <t>dc_falls</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -6501,17 +6597,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>SL_004</t>
+          <t>CX_005</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>VERMONT LIBERATED</t>
+          <t>GETTYSBURG TAKEN</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>vermont_liberated</t>
+          <t>gettysburg_lost</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
@@ -6534,22 +6630,22 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>PROT_01_SUMMON</t>
+          <t>SL_001</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>MOTHMAN APPROACHES</t>
+          <t>PENNSYLVANIA FULLY LIBERATED</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>mothman_approach</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>pa_liberated</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F49" s="22" t="inlineStr">
@@ -6557,11 +6653,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>kinky_lewd</t>
-        </is>
-      </c>
+      <c r="G49" s="14" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
@@ -6571,22 +6663,22 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>PROT_14_SUMMON</t>
+          <t>SL_004</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>MOUNT RUSHMORE AWAKENS</t>
+          <t>VERMONT LIBERATED</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>rushmore_awakens</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>vermont_liberated</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F50" s="22" t="inlineStr">
@@ -6594,11 +6686,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>kinky_lewd</t>
-        </is>
-      </c>
+      <c r="G50" s="14" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
@@ -6608,22 +6696,22 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>PROT_02_SUMMON</t>
+          <t>PROT_01_SUMMON</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>JERSEY DEVIL EMERGES FROM THE PINE BARRENS</t>
+          <t>MOTHMAN APPROACHES</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>jersey_devil</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>mothman_approach</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F51" s="22" t="inlineStr">
@@ -6633,7 +6721,7 @@
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>kinky_lewd</t>
         </is>
       </c>
     </row>
@@ -6645,22 +6733,22 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>PROT_03_SUMMON</t>
+          <t>PROT_14_SUMMON</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>BIGFOOT SIDES WITH THE REVOLUTION</t>
+          <t>MOUNT RUSHMORE AWAKENS</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>bigfoot</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>rushmore_awakens</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F52" s="22" t="inlineStr">
@@ -6670,7 +6758,7 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>kinky_lewd</t>
         </is>
       </c>
     </row>
@@ -6682,17 +6770,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>PROT_04_SUMMON</t>
+          <t>PROT_02_SUMMON</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>THUNDERBIRD ANSWERS THE CALL</t>
+          <t>JERSEY DEVIL EMERGES FROM THE PINE BARRENS</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>thunderbird</t>
+          <t>jersey_devil</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -6719,17 +6807,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>PROT_05_SUMMON</t>
+          <t>PROT_03_SUMMON</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>THE HORSEMAN RIDES AGAIN</t>
+          <t>BIGFOOT SIDES WITH THE REVOLUTION</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>headless_horseman</t>
+          <t>bigfoot</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
@@ -6756,17 +6844,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>PROT_06_SUMMON</t>
+          <t>PROT_04_SUMMON</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>CHESSIE RISES FROM THE BAY</t>
+          <t>THUNDERBIRD ANSWERS THE CALL</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>chessie</t>
+          <t>thunderbird</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -6793,17 +6881,17 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>PROT_07_SUMMON</t>
+          <t>PROT_05_SUMMON</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>THE BELL WITCH MANIFESTS IN TENNESSEE</t>
+          <t>THE HORSEMAN RIDES AGAIN</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>bell_witch</t>
+          <t>headless_horseman</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
@@ -6830,17 +6918,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>PROT_08_SUMMON</t>
+          <t>PROT_06_SUMMON</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES RETURNS TO SERVICE</t>
+          <t>CHESSIE RISES FROM THE BAY</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>old_ironsides</t>
+          <t>chessie</t>
         </is>
       </c>
       <c r="E57" s="14" t="inlineStr">
@@ -6867,17 +6955,17 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>PROT_09_SUMMON</t>
+          <t>PROT_07_SUMMON</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>THE GUARDIAN OF VALLEY FORGE STIRS</t>
+          <t>THE BELL WITCH MANIFESTS IN TENNESSEE</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>valley_forge_guardian</t>
+          <t>bell_witch</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
@@ -6904,17 +6992,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>PROT_10_SUMMON</t>
+          <t>PROT_08_SUMMON</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>THE SNALLYGASTER DESCENDS ON MARYLAND</t>
+          <t>OLD IRONSIDES RETURNS TO SERVICE</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>snallygaster</t>
+          <t>old_ironsides</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
@@ -6941,17 +7029,17 @@
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>PROT_11_SUMMON</t>
+          <t>PROT_09_SUMMON</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>PAUL REVERE RIDES AGAIN</t>
+          <t>THE GUARDIAN OF VALLEY FORGE STIRS</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>paul_revere</t>
+          <t>valley_forge_guardian</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
@@ -6978,17 +7066,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>PROT_12_SUMMON</t>
+          <t>PROT_10_SUMMON</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>THE LIBERTY BELL RINGS</t>
+          <t>THE SNALLYGASTER DESCENDS ON MARYLAND</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>liberty_bell_ring</t>
+          <t>snallygaster</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
@@ -7015,17 +7103,17 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>PROT_13_SUMMON</t>
+          <t>PROT_11_SUMMON</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>THE GREEN MOUNTAIN GHOST RIDES</t>
+          <t>PAUL REVERE RIDES AGAIN</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>green_mountain_ghost</t>
+          <t>paul_revere</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
@@ -7052,17 +7140,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>PROT_15_SUMMON</t>
+          <t>PROT_12_SUMMON</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>THE SKUNK APE EMERGES FROM FLORIDA</t>
+          <t>THE LIBERTY BELL RINGS</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>skunk_ape</t>
+          <t>liberty_bell_ring</t>
         </is>
       </c>
       <c r="E63" s="14" t="inlineStr">
@@ -7089,17 +7177,17 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>PROT_16_SUMMON</t>
+          <t>PROT_13_SUMMON</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN IS READY</t>
+          <t>THE GREEN MOUNTAIN GHOST RIDES</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>eternal_minuteman</t>
+          <t>green_mountain_ghost</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -7126,17 +7214,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>PROT_17_SUMMON</t>
+          <t>PROT_15_SUMMON</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>LINCOLN'S GHOST APPEARS IN WASHINGTON</t>
+          <t>THE SKUNK APE EMERGES FROM FLORIDA</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>lincolns_ghost</t>
+          <t>skunk_ape</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -7163,17 +7251,17 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>FORT_001</t>
+          <t>PROT_16_SUMMON</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>FORT [TILE_NAME]: STRUCTURAL CONCERNS AND A PAMPHLET PROBLEM</t>
+          <t>THE MINUTEMAN IS READY</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>fort_pamphlets</t>
+          <t>eternal_minuteman</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -7186,7 +7274,11 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G66" s="14" t="inlineStr"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
@@ -7196,17 +7288,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>FORT_003</t>
+          <t>PROT_17_SUMMON</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE FIRES [COMMANDER_NAME] IN FRONT OF GOD AND THE GARRISON</t>
+          <t>LINCOLN'S GHOST APPEARS IN WASHINGTON</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>fort_confrontation</t>
+          <t>lincolns_ghost</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
@@ -7219,7 +7311,11 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
@@ -7229,17 +7325,17 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>FORT_004</t>
+          <t>FORT_001</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>FORT [TILE_NAME] REPAIR ORDER SIGNED — GRIEVANCES RESOLVED</t>
+          <t>FORT [TILE_NAME]: STRUCTURAL CONCERNS AND A PAMPHLET PROBLEM</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>fort_handshake</t>
+          <t>fort_pamphlets</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
@@ -7262,17 +7358,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>FORT_005</t>
+          <t>FORT_003</t>
         </is>
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME]</t>
+          <t>PRESIDENT CARLISLE FIRES [COMMANDER_NAME] IN FRONT OF GOD AND THE GARRISON</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>fort_diplomatic</t>
+          <t>fort_confrontation</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
@@ -7295,17 +7391,17 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>COLLAPSE_01</t>
+          <t>FORT_004</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>THE REPUBLIC HAS FALLEN</t>
+          <t>FORT [TILE_NAME] REPAIR ORDER SIGNED — GRIEVANCES RESOLVED</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>collapse_republic</t>
+          <t>fort_handshake</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -7328,17 +7424,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>COLLAPSE_02</t>
+          <t>FORT_005</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>WASHINGTON STANDS ALONE</t>
+          <t>CLASSIFIED DIPLOMATIC PROCEEDINGS AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>ualani_washington</t>
+          <t>fort_diplomatic</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -7361,17 +7457,17 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>STATE_REBEL_01</t>
+          <t>COLLAPSE_01</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>STATE DECLARES INDEPENDENCE: [TILE_NAME] RAISES A NEW FLAG</t>
+          <t>THE REPUBLIC HAS FALLEN</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>state_secession</t>
+          <t>collapse_republic</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
@@ -7394,17 +7490,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>STATE_REINTEGRATED_01</t>
+          <t>COLLAPSE_02</t>
         </is>
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>[TILE_NAME] RETURNS TO THE REPUBLIC</t>
+          <t>WASHINGTON STANDS ALONE</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>state_reintegration</t>
+          <t>ualani_washington</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -7427,17 +7523,17 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>HARVEST_001</t>
+          <t>STATE_REBEL_01</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>THE ARMY ATE THE SEED CORN</t>
+          <t>STATE DECLARES INDEPENDENCE: [TILE_NAME] RAISES A NEW FLAG</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>harvest_crisis</t>
+          <t>state_secession</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -7460,17 +7556,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>HARVEST_VISIT_01</t>
+          <t>STATE_REINTEGRATED_01</t>
         </is>
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE SAVES THE HARVEST</t>
+          <t>[TILE_NAME] RETURNS TO THE REPUBLIC</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>harvest_complete</t>
+          <t>state_reintegration</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -7493,17 +7589,17 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>HARBOR_001</t>
+          <t>HARVEST_001</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>CROWN VESSELS SPOTTED IN TERRITORIAL WATERS: DOCK AT [TILE_NAME] AT RISK</t>
+          <t>THE ARMY ATE THE SEED CORN</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>harbor_threat</t>
+          <t>harvest_crisis</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -7526,17 +7622,17 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>HARBOR_ESCORT_01</t>
+          <t>HARVEST_VISIT_01</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>HARBOR SECURED: CROWN FRIGATE RETREATS FROM [TILE_NAME]</t>
+          <t>PRESIDENT CARLISLE SAVES THE HARVEST</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>harbor_secure</t>
+          <t>harvest_complete</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
@@ -7559,17 +7655,17 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>HARBOR_BURN_01</t>
+          <t>HARBOR_001</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>DOCK FACILITIES AT [TILE_NAME] DESTROYED: ACCESS DENIED TO ALL PARTIES</t>
+          <t>CROWN VESSELS SPOTTED IN TERRITORIAL WATERS: DOCK AT [TILE_NAME] AT RISK</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>harbor_burned</t>
+          <t>harbor_threat</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -7592,17 +7688,17 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>FORGE_001</t>
+          <t>HARBOR_ESCORT_01</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>INTELLIGENCE ALERT: CROWN FORCES HAVE LOCATED THE FORGE AT [TILE_NAME]</t>
+          <t>HARBOR SECURED: CROWN FRIGATE RETREATS FROM [TILE_NAME]</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>forge_threat</t>
+          <t>harbor_secure</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -7625,17 +7721,17 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>FORGE_REINFORCE_01</t>
+          <t>HARBOR_BURN_01</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>FORGE SECURED: CROWN ASSAULT PLAN ABANDONED</t>
+          <t>DOCK FACILITIES AT [TILE_NAME] DESTROYED: ACCESS DENIED TO ALL PARTIES</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>forge_secure</t>
+          <t>harbor_burned</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -7658,17 +7754,17 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>FORGE_EVACUATE_01</t>
+          <t>FORGE_001</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>EMERGENCY EXTRACTION: WEAPONS CACHE SECURED — FORGE TEMPORARILY OUT OF SERVICE</t>
+          <t>INTELLIGENCE ALERT: CROWN FORCES HAVE LOCATED THE FORGE AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>forge_evac</t>
+          <t>forge_threat</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -7691,17 +7787,17 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>CORRUPT_001</t>
+          <t>FORGE_REINFORCE_01</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>MAGISTRATE [COMMANDER_NAME] UNDER INVESTIGATION FOR REMARKABLE CONDUCT</t>
+          <t>FORGE SECURED: CROWN ASSAULT PLAN ABANDONED</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>corruption_crisis</t>
+          <t>forge_secure</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
@@ -7724,17 +7820,17 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>CORRUPT_TRIAL_01</t>
+          <t>FORGE_EVACUATE_01</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>MAGISTRATE REMOVED IN DISGRACE — [TILE_NAME] COURTHOUSE CLEANED</t>
+          <t>EMERGENCY EXTRACTION: WEAPONS CACHE SECURED — FORGE TEMPORARILY OUT OF SERVICE</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>corrupt_trial</t>
+          <t>forge_evac</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
@@ -7757,17 +7853,17 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>CORRUPT_REFORM_01</t>
+          <t>CORRUPT_001</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>COURTHOUSE REFORMS UNDERWAY AT [TILE_NAME]</t>
+          <t>MAGISTRATE [COMMANDER_NAME] UNDER INVESTIGATION FOR REMARKABLE CONDUCT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>courthouse_reform</t>
+          <t>corruption_crisis</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
@@ -7790,17 +7886,17 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>CORRUPT_DEAL_01</t>
+          <t>CORRUPT_TRIAL_01</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>ARRANGEMENT REACHED AT [TILE_NAME]: COURTHOUSE CONTINUES OPERATING</t>
+          <t>MAGISTRATE REMOVED IN DISGRACE — [TILE_NAME] COURTHOUSE CLEANED</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>corrupt_deal</t>
+          <t>corrupt_trial</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
@@ -7823,17 +7919,17 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>BORDER_001</t>
+          <t>CORRUPT_REFORM_01</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>CANADIAN BORDER INCIDENT AT [TILE_NAME]: THE LINE IS IN QUESTION</t>
+          <t>COURTHOUSE REFORMS UNDERWAY AT [TILE_NAME]</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>border_dispute</t>
+          <t>courthouse_reform</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
@@ -7856,17 +7952,17 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>BORDER_ASSERT_01</t>
+          <t>CORRUPT_DEAL_01</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>FEDERAL BOUNDARY MARKER PLANTED AT [TILE_NAME]: CANADA FILES OBJECTION</t>
+          <t>ARRANGEMENT REACHED AT [TILE_NAME]: COURTHOUSE CONTINUES OPERATING</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>border_assert</t>
+          <t>corrupt_deal</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
@@ -7889,17 +7985,17 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>BORDER_SURVEY_01</t>
+          <t>BORDER_001</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>SURVEY COMPLETE AT [TILE_NAME]: THE LAND HAS BEEN MEASURED AND IS OURS</t>
+          <t>CANADIAN BORDER INCIDENT AT [TILE_NAME]: THE LINE IS IN QUESTION</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>border_survey</t>
+          <t>border_dispute</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -7922,17 +8018,17 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>GARRISON_001</t>
+          <t>BORDER_ASSERT_01</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>FIELD REPORT: [TILE_NAME] GARRISON REPORTING CRITICAL SUPPLY SHORTFALL</t>
+          <t>FEDERAL BOUNDARY MARKER PLANTED AT [TILE_NAME]: CANADA FILES OBJECTION</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>garrison_starving</t>
+          <t>border_assert</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -7955,17 +8051,17 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>CRISIS_CLAIM_001</t>
+          <t>BORDER_SURVEY_01</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>LEGITIMACY CRISIS: THE REPUBLIC'S CLAIM ON ITSELF IS IN QUESTION</t>
+          <t>SURVEY COMPLETE AT [TILE_NAME]: THE LAND HAS BEEN MEASURED AND IS OURS</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>legitimacy_crisis</t>
+          <t>border_survey</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -7988,17 +8084,17 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>TURNCOAT_001</t>
+          <t>GARRISON_001</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>INTELLIGENCE REPORT: COMMANDER [COMMANDER_NAME] MAY BE IN CONTACT WITH THE CROWN</t>
+          <t>FIELD REPORT: [TILE_NAME] GARRISON REPORTING CRITICAL SUPPLY SHORTFALL</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>turncoat_report</t>
+          <t>garrison_starving</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
@@ -8021,17 +8117,17 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>MEMORIAL_001</t>
+          <t>CRISIS_CLAIM_001</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>[TILE_NAME] FALLS TO THE CROWN: HISTORICAL SITE UNDER OCCUPATION</t>
+          <t>LEGITIMACY CRISIS: THE REPUBLIC'S CLAIM ON ITSELF IS IN QUESTION</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>memorial_lost</t>
+          <t>legitimacy_crisis</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -8054,30 +8150,392 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
+          <t>TURNCOAT_001</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>INTELLIGENCE REPORT: COMMANDER [COMMANDER_NAME] MAY BE IN CONTACT WITH THE CROWN</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>turncoat_report</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>MEMORIAL_001</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>[TILE_NAME] FALLS TO THE CROWN: HISTORICAL SITE UNDER OCCUPATION</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>memorial_lost</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
           <t>MEMORIAL_RESTORE_01</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>[TILE_NAME] LIBERATED: THE MEMORIAL IS OURS AGAIN</t>
         </is>
       </c>
-      <c r="D93" s="15" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>memorial_restored</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F93" s="22" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr"/>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_SUMMON</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>LE WENDIGO WAKES IN THE LAURENTIAN FOREST</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>wendigo_approach</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_02_SUMMON</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>LE LOUP-GAROU RUNS THE RIVER ROAD — RIVIÈRE-DU-LOUP QUARANTINED</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>loup_garou</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_SUMMON</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>LES FEUX FOLLETS RISE OVER THE SAINT JOHN MARSHES — NAVIGATION DISRUPTED</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>feux_follets</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_SUMMON</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>MISHEPESHU STIRS BENEATH LAKE SIMCOE — CROSSINGS CONTESTED</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>mishepeshu</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_05_SUMMON</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>LA CORRIVEAU IS FREE — THE IRON CAGE HAS BEEN SWINGING IN TROIS-PISTOLES</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>la_corriveau</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_06_SUMMON</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>LE CARCAJOU MOVES THROUGH THE MONCTON FOREST — NOTHING STOPS IT</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>carcajou</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_SUMMON</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>THE FLYING CANOE RUNS THE OTTAWA RIVER — THREE SIGHTINGS TWO MISSING PATROLS</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>chasse_galerie</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_SUMMON</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>THE GOUGOU RISES IN THE CHALEUR BAY — CHAMPLAIN'S MONSTER IS REAL</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>le_gougou</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F103" s="22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8129,7 +8587,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>154</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -8139,7 +8597,7 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>107 rows</t>
+          <t>154 rows</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8609,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -8161,7 +8619,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>209 rows</t>
+          <t>304 rows</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8653,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -8205,7 +8663,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>58 rows</t>
+          <t>60 rows</t>
         </is>
       </c>
     </row>

--- a/project_masterdoc.xlsx
+++ b/project_masterdoc.xlsx
@@ -8587,7 +8587,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>250</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>154 rows</t>
+          <t>250 rows</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>434</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>304 rows</t>
+          <t>434 rows</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>35 rows</t>
+          <t>83 rows</t>
         </is>
       </c>
     </row>

--- a/project_masterdoc.xlsx
+++ b/project_masterdoc.xlsx
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>sensual</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>kinky_lewd</t>
+          <t>kinky</t>
         </is>
       </c>
       <c r="D22" s="37" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>kinky_lewd</t>
+          <t>kinky</t>
         </is>
       </c>
       <c r="D35" s="37" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>The Night Mark Penoit Took You on the River and Told You the Full Story of How He Secured the Canoe for the Republic</t>
+          <t>The Night Marc Penoit Took You on the River and Told You the Full Story of How He Secured the Canoe for the Republic</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>The Night After the Peace Was Signed — Ualani Carlisle and Jessica Clear-Water Celebrate Alone</t>
+          <t>The Night After the Peace Was Signed — Ualani Carlisle and Jessica Commanda Odjick Celebrate Alone</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">

--- a/project_masterdoc.xlsx
+++ b/project_masterdoc.xlsx
@@ -2632,7 +2632,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>PROT_01–17: each has PROT_xx_SUMMON → PROT_xx_TAME → PROT_xx_AGREE. SUMMON fires via _check_protector_summons() with wild corruption risk 25%/turn. All 17 protectors: Mothman, Jersey Devil, Bigfoot, Thunderbird, Headless Horseman, Chessie, Bell Witch, Old Ironsides, Valley Forge Spirit, Snallygaster, Paul Revere, Liberty Bell, Green Mountain Boys, Mount Rushmore Spirits, Skunk Ape, Eternal Minuteman, Lincoln's Ghost. Staggered turn thresholds per protector.</t>
+          <t>PROT_01–17: each has PROT_xx_SUMMON → PROT_xx_TAME → PROT_xx_AGREE. SUMMON fires via _check_protector_summons() with wild corruption risk 25%/turn. All 17 protectors: Mothman, Jersey Devil, Bigfoot, Thunderbird, Headless Horseman, Chessie, Bell Witch, Old Ironsides, Valley Forge Spirit, Snallygaster, Paul Revere, Liberty Bell, Green Mountain Boys, Skunk Ape, Eternal Minuteman, Lincoln's Ghost. Staggered turn thresholds per protector.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>CMD_THANKS (explicit), FORT_005 (explicit), PROT_01_SUMMON (kinky_lewd), CAN_PEACE_01 (explicit), WH_SECRET_07 (explicit). PROT_01_AGREE, PROT_14_AGREE, PROT_14_SUMMON also kinky_lewd flagged.</t>
+          <t>CMD_THANKS (explicit), FORT_005 (explicit), PROT_01_SUMMON (kinky_lewd), CAN_PEACE_01 (explicit), WH_SECRET_07 (explicit). PROT_01_AGREE also kinky_lewd flagged.</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>morale_boost</t>
+          <t>trigger_event → CMD_THANKS_INTIMATE</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OLD IRONSIDES FORMALLY JOINS THE CONTINENTAL NAVY</t>
+          <t>President Ualani Sets Sail</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
@@ -5020,51 +5020,51 @@
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
-        <is>
-          <t>PROT_14_AGREE</t>
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>PROT_15_AGREE</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>THE RUSHMORE COUNCIL FORMALLY ENDORSES PRESIDENT CARLISLE</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="inlineStr">
-        <is>
-          <t>kinky</t>
-        </is>
-      </c>
-      <c r="D35" s="37" t="inlineStr">
-        <is>
-          <t>kinky_lewd</t>
+          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENTAL REPUBLIC</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>explicit</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>The Complete Presidential Council</t>
+          <t>The Full Everglades Accord</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>set_flag → prot_14_agreed</t>
+          <t>set_flag → prot_15_agreed</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>PROT_14_A_BTN2</t>
+          <t>PROT_15_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>PROT_15_AGREE</t>
+          <t>PROT_16_AGREE</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>SKUNK APE FORMALLY PATROLS FLORIDA FOR THE CONTINENTAL REPUBLIC</t>
+          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL REPUBLIC</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
@@ -5079,29 +5079,29 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>The Full Everglades Accord</t>
+          <t>The Full Lexington Green Ceremony</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>set_flag → prot_15_agreed</t>
+          <t>set_flag → prot_16_agreed</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>PROT_15_A_BTN2</t>
+          <t>PROT_16_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>PROT_16_AGREE</t>
+          <t>PROT_17_AGREE</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>THE MINUTEMAN FORMALLY DECLARES FOR THE CONTINENTAL REPUBLIC</t>
+          <t>LINCOLN'S GHOST TOURS THE MALL</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
@@ -5116,29 +5116,29 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>The Full Lexington Green Ceremony</t>
+          <t>Invite the President to Dinner this evening</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>set_flag → prot_16_agreed</t>
+          <t>trigger_event → PROT_17_AGREE_INTIMATE</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>PROT_16_A_BTN2</t>
+          <t>PROT_17_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>PROT_17_AGREE</t>
+          <t>STUMP_SPEECH_01</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>LINCOLN FORMALLY ENDORSES PRESIDENT CARLISLE'S ADMINISTRATION</t>
+          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — THE CAMPAIGN IS HERE</t>
         </is>
       </c>
       <c r="C38" s="34" t="inlineStr">
@@ -5153,81 +5153,81 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>The Full Presidential Consultation</t>
+          <t>The Full Presidential Address</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>set_flag → prot_17_agreed</t>
+          <t>election_pressure_change</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>PROT_17_A_BTN2</t>
+          <t>STUMP_BTN2</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="33" t="inlineStr">
-        <is>
-          <t>STUMP_SPEECH_01</t>
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>VP_DOUBT</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>PRESIDENT CARLISLE TAKES THE FLOOR AT [TILE_NAME] — THE CAMPAIGN IS HERE</t>
-        </is>
-      </c>
-      <c r="C39" s="34" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
+          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QUESTIONING EVERYTHING</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Remind Them in a More Convincing Way</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>morale_boost</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>VP_DOUBT_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>VP_BATTLEFIELD</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAME] AT THE FRONT LINE</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>The Full Presidential Address</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>election_pressure_change</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>STUMP_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>VP_DOUBT</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>THE VICE PRESIDENT AT 2 A.M.: [COMMANDER_NAME] IS QUESTIONING EVERYTHING</t>
-        </is>
-      </c>
-      <c r="C40" s="39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D40" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Remind Them in a More Convincing Way</t>
+          <t>More Than Standing Beside Them</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -5237,19 +5237,19 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>VP_DOUBT_BTN2</t>
+          <t>VP_BATTLEFIELD_BTN2</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="33" t="inlineStr">
         <is>
-          <t>VP_BATTLEFIELD</t>
+          <t>VP_PRE_ELECTION</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT PICKS UP A MUSKET: [COMMANDER_NAME] AT THE FRONT LINE</t>
+          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [COMMANDER_NAME] ISN'T SURE THEY WANT TO RUN</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>More Than Standing Beside Them</t>
+          <t>Convince Them to Stay In the Race</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>VP_BATTLEFIELD_BTN2</t>
+          <t>VP_PRE_ELECTION_BTN2</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>VP_PRE_ELECTION</t>
+          <t>VP_LEGACY</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT CALLS AN UNSCHEDULED MEETING — [COMMANDER_NAME] ISN'T SURE THEY WANT TO RUN</t>
+          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Convince Them to Stay In the Race</t>
+          <t>This Has Always Been Personal</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -5311,98 +5311,98 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>VP_PRE_ELECTION_BTN2</t>
+          <t>VP_LEGACY_BTN2</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="33" t="inlineStr">
-        <is>
-          <t>VP_LEGACY</t>
+      <c r="A43" s="38" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_01</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>THE VICE PRESIDENT LEAVES A NOTE — [COMMANDER_NAME] HAS SOMETHING TO SAY</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
+          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUTSIDE OFFICIAL CHANNELS</t>
+        </is>
+      </c>
+      <c r="C43" s="39" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="D43" s="21" t="inlineStr">
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Answer the Way the Question Was Really Asked</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>set_flag → can_clearwater_close</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CAN_CLEARWATER_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>CAN_JOINT_OPS_01</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE ONE MAP</t>
+        </is>
+      </c>
+      <c r="C44" s="34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>This Has Always Been Personal</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>The Full Joint Operation — All Three Committed</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>morale_boost</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>VP_LEGACY_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="38" t="inlineStr">
-        <is>
-          <t>CAN_CLEARWATER_01</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>PM CLEAR-WATER'S PRIVATE CHANNEL: JESSICA WRITES OUTSIDE OFFICIAL CHANNELS</t>
-        </is>
-      </c>
-      <c r="C44" s="39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D44" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Answer the Way the Question Was Really Asked</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>set_flag → can_clearwater_close</t>
-        </is>
-      </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CAN_CLEARWATER_BTN2</t>
+          <t>CAN_JOINT_OPS_BTN2</t>
         </is>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="33" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_01</t>
+          <t>CAN_SUMMIT_01</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>JOINT INTELLIGENCE SUMMIT: THREE GOVERNMENTS SHARE ONE MAP</t>
+          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR THE FIRST TIME</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="D45" s="21" t="inlineStr">
@@ -5412,29 +5412,29 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>The Full Joint Operation — All Three Committed</t>
+          <t>The Full Ottawa Summit — All Diplomatic Protocols Observed</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>morale_boost</t>
+          <t>set_flag → can_summit_complete</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CAN_JOINT_OPS_BTN2</t>
+          <t>CAN_SUMMIT_BTN2</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="33" t="inlineStr">
         <is>
-          <t>CAN_SUMMIT_01</t>
+          <t>CAN_ALLIANCE_SIGNED</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>THE OTTAWA SUMMIT: ALL THREE IN THE SAME ROOM FOR THE FIRST TIME</t>
+          <t>THE CONTINENTAL DEFENSE ALLIANCE IS SIGNED: THREE NATIONS — ONE FRONT</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
@@ -5449,29 +5449,29 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>The Full Ottawa Summit — All Diplomatic Protocols Observed</t>
+          <t>The Full Ratification Ceremony — All Three in Agreement</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>set_flag → can_summit_complete</t>
+          <t>form_alliance → CA</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CAN_SUMMIT_BTN2</t>
+          <t>CAN_ALLIANCE_BTN2</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="33" t="inlineStr">
         <is>
-          <t>CAN_ALLIANCE_SIGNED</t>
+          <t>CAN_PEACE_01</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>THE CONTINENTAL DEFENSE ALLIANCE IS SIGNED: THREE NATIONS — ONE FRONT</t>
+          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO WASHINGTON</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
@@ -5486,103 +5486,103 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>The Full Ratification Ceremony — All Three in Agreement</t>
+          <t>The Full Continental Peace Proceedings</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>form_alliance → CA</t>
+          <t>morale_boost</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CAN_ALLIANCE_BTN2</t>
+          <t>CAN_PEACE_BTN2</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="33" t="inlineStr">
-        <is>
-          <t>CAN_PEACE_01</t>
+      <c r="A48" s="38" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_LUCK</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>THE TIDE HAS TURNED: PENOIT AND CLEAR-WATER COME TO WASHINGTON</t>
-        </is>
-      </c>
-      <c r="C48" s="34" t="inlineStr">
+          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY BEFORE THE ELECTION</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Say the Thing That Cannot Be Said After the Results</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>election_pressure_change</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CAN_ELECTION_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>CA_PROT_01_AGREE</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
+        </is>
+      </c>
+      <c r="C49" s="34" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="D48" s="21" t="inlineStr">
+      <c r="D49" s="21" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>The Full Continental Peace Proceedings</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>morale_boost</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>CAN_PEACE_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="38" t="inlineStr">
-        <is>
-          <t>CAN_ELECTION_LUCK</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>PM CLEAR-WATER'S CALL: JESSICA HAS SOMETHING TO SAY BEFORE THE ELECTION</t>
-        </is>
-      </c>
-      <c r="C49" s="39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Say the Thing That Cannot Be Said After the Results</t>
+          <t>The Full Meeting with Jessica Afterward — What She Wasn't Putting in Dispatches</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>election_pressure_change</t>
+          <t>set_flag → ca_prot_01_agreed</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CAN_ELECTION_BTN2</t>
+          <t>CA_PROT_01_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="33" t="inlineStr">
         <is>
-          <t>CA_PROT_01_AGREE</t>
+          <t>CA_PROT_02_AGREE</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>LE WENDIGO STANDS DOWN: SAINT-GEORGES FOREST ACCORD</t>
+          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
@@ -5597,103 +5597,103 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>The Full Meeting with Jessica Afterward — What She Wasn't Putting in Dispatches</t>
+          <t>The Night the Wolf Stopped Running — What Clear-Water Told You Privately</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>set_flag → ca_prot_01_agreed</t>
+          <t>set_flag → ca_prot_02_agreed</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CA_PROT_01_A_BTN2</t>
+          <t>CA_PROT_02_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="33" t="inlineStr">
-        <is>
-          <t>CA_PROT_02_AGREE</t>
+      <c r="A51" s="38" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_AGREE</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>LE LOUP-GAROU OF RIVIÈRE-DU-LOUP: FORMALLY ACKNOWLEDGED BY THE REPUBLIC</t>
-        </is>
-      </c>
-      <c r="C51" s="34" t="inlineStr">
+          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="D51" s="21" t="inlineStr">
+      <c r="D51" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>The Night Jessica Walked You Through the Marsh Herself to Show You What the Lights Mean</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>set_flag → ca_prot_03_agreed</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CA_PROT_03_A_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="33" t="inlineStr">
+        <is>
+          <t>CA_PROT_04_AGREE</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>The Night the Wolf Stopped Running — What Clear-Water Told You Privately</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>set_flag → ca_prot_02_agreed</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>CA_PROT_02_A_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="38" t="inlineStr">
-        <is>
-          <t>CA_PROT_03_AGREE</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>LES FEUX FOLLETS FORMALLY ACKNOWLEDGED: THE SAINT JOHN MARSH ACCORD</t>
-        </is>
-      </c>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D52" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>The Night Jessica Walked You Through the Marsh Herself to Show You What the Lights Mean</t>
+          <t>What Jessica Said Afterward About Why This One Required the Republic to Apologize First</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>set_flag → ca_prot_03_agreed</t>
+          <t>set_flag → ca_prot_04_agreed</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CA_PROT_03_A_BTN2</t>
+          <t>CA_PROT_04_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="33" t="inlineStr">
         <is>
-          <t>CA_PROT_04_AGREE</t>
+          <t>CA_PROT_05_AGREE</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>MISHEPESHU PACT FORMALIZED: THE GREAT LYNX HOLDS THE ONTARIO WATERWAYS</t>
+          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THREE GARRISONS EVACUATED THIS WEEK</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -5708,29 +5708,29 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>What Jessica Said Afterward About Why This One Required the Republic to Apologize First</t>
+          <t>What Jessica Told You About What Corriveau Actually Wanted to Say — The Thing Not in the Dispatches</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>set_flag → ca_prot_04_agreed</t>
+          <t>set_flag → ca_prot_05_agreed</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CA_PROT_04_A_BTN2</t>
+          <t>CA_PROT_05_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t>CA_PROT_05_AGREE</t>
+          <t>CA_PROT_06_AGREE</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>LA CORRIVEAU FORMALLY ALLIES WITH THE REPUBLIC — THREE GARRISONS EVACUATED THIS WEEK</t>
+          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -5745,140 +5745,140 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>What Jessica Told You About What Corriveau Actually Wanted to Say — The Thing Not in the Dispatches</t>
+          <t>The Private Briefing — What Clear-Water Told You About Why the Carcajou Actually Accepted the Accord</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>set_flag → ca_prot_05_agreed</t>
+          <t>set_flag → ca_prot_06_agreed</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CA_PROT_05_A_BTN2</t>
+          <t>CA_PROT_06_A_BTN2</t>
         </is>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="33" t="inlineStr">
-        <is>
-          <t>CA_PROT_06_AGREE</t>
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_AGREE</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>LE CARCAJOU FORMALLY RECOGNIZED: THE MONCTON CORRIDOR ACCORD</t>
-        </is>
-      </c>
-      <c r="C55" s="34" t="inlineStr">
+          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="D55" s="21" t="inlineStr">
+      <c r="D55" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>The Night Marc Penoit Took You on the River and Told You the Full Story of How He Secured the Canoe for the Republic</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>set_flag → ca_prot_07_agreed</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CA_PROT_07_A_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_AGREE</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE CONTINENTAL ALLIANCE</t>
+        </is>
+      </c>
+      <c r="C56" s="34" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
         <is>
           <t>explicit</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>The Private Briefing — What Clear-Water Told You About Why the Carcajou Actually Accepted the Accord</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>set_flag → ca_prot_06_agreed</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>CA_PROT_06_A_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="38" t="inlineStr">
-        <is>
-          <t>CA_PROT_07_AGREE</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>LA CHASSE-GALERIE: THE RIVER RUNS FOR THE REPUBLIC NOW</t>
-        </is>
-      </c>
-      <c r="C56" s="39" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>What Jessica Told You About the Gougou's Real Name — and What It Cost Her to Learn It</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>set_flag → ca_prot_08_agreed</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CA_PROT_08_A_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t>PEACE_ALLIED_01</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="D56" s="40" t="inlineStr">
+      <c r="D57" s="40" t="inlineStr">
         <is>
           <t>sensual</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>The Night Marc Penoit Took You on the River and Told You the Full Story of How He Secured the Canoe for the Republic</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>set_flag → ca_prot_07_agreed</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>CA_PROT_07_A_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="33" t="inlineStr">
-        <is>
-          <t>CA_PROT_08_AGREE</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>THE GOUGOU FORMALLY GUARDS THE CHALEUR BAY FOR THE CONTINENTAL ALLIANCE</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>standard</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>explicit</t>
-        </is>
-      </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>What Jessica Told You About the Gougou's Real Name — and What It Cost Her to Learn It</t>
+          <t>The Night After the Peace Was Signed — Ualani Carlisle and Jessica Commanda Odjick Celebrate Alone</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>set_flag → ca_prot_08_agreed</t>
+          <t>set_flag → peace_allied_signed</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CA_PROT_08_A_BTN2</t>
+          <t>PEACE_ALLIED_BTN2</t>
         </is>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="38" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_01</t>
+          <t>PEACE_USA_01</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE CROWN EXPELLED FROM THE CONTINENT</t>
+          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
         </is>
       </c>
       <c r="C58" s="39" t="inlineStr">
@@ -5893,192 +5893,192 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>The Night After the Peace Was Signed — Ualani Carlisle and Jessica Commanda Odjick Celebrate Alone</t>
+          <t>Ualani Carlisle Marks the End of the War in Her Own Way — Alone in the President's Office at Dawn</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>set_flag → peace_allied_signed</t>
+          <t>set_flag → peace_usa_signed</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>PEACE_ALLIED_BTN2</t>
+          <t>PEACE_USA_BTN2</t>
         </is>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="38" t="inlineStr">
         <is>
-          <t>PEACE_USA_01</t>
+          <t>WH_SECRET_01</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>PEACE OF [TILE_NAME] — THE REPUBLIC HAS EXPELLED THE CROWN</t>
+          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES THE NEW YEAR ALONE</t>
         </is>
       </c>
       <c r="C59" s="39" t="inlineStr">
         <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>sensual</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>The Long Night of the New Year — What She Does with the Bottle and the Quiet</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>morale_boost</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>WH_SECRET_01_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>INDEPENDENCE DAY AT THE WHITE HOUSE — THE REPUBLIC CELEBRATES</t>
+        </is>
+      </c>
+      <c r="C60" s="34" t="inlineStr">
+        <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="D59" s="40" t="inlineStr">
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>The Night She Decided the Republic Was Worth Fighting For — and How She Spent It</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>morale_boost</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>WH_SECRET_07_BTN2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="38" t="inlineStr">
+        <is>
+          <t>WH_SECRET_10</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESSICA CLEAR-WATER ARRIVES</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="inlineStr">
         <is>
           <t>sensual</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>Ualani Carlisle Marks the End of the War in Her Own Way — Alone in the President's Office at Dawn</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>set_flag → peace_usa_signed</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>PEACE_USA_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="38" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>THE WHITE HOUSE AT MIDNIGHT — THE PRESIDENT WATCHES THE NEW YEAR ALONE</t>
-        </is>
-      </c>
-      <c r="C60" s="39" t="inlineStr">
+      <c r="D61" s="40" t="inlineStr">
         <is>
           <t>sensual</t>
         </is>
       </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>The Long Night of the New Year — What She Does with the Bottle and the Quiet</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>morale_boost</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>WH_SECRET_01_BTN2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="33" t="inlineStr">
-        <is>
-          <t>WH_SECRET_07</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>JULY AT THE WHITE HOUSE — INDEPENDENCE DAY IS ALSO HERS</t>
-        </is>
-      </c>
-      <c r="C61" s="34" t="inlineStr">
-        <is>
-          <t>explicit</t>
-        </is>
-      </c>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>explicit</t>
-        </is>
-      </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>The Night She Decided the Republic Was Worth Fighting For — and How She Spent It</t>
+          <t>What Ualani Writes Back — and What She Does Not Put in the Letter but Means</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>morale_boost</t>
+          <t>nothing</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>WH_SECRET_07_BTN2</t>
+          <t>WH_SECRET_10_BTN2</t>
         </is>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="38" t="inlineStr">
         <is>
-          <t>WH_SECRET_10</t>
+          <t>WH_SECRET_12</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>INDIGENOUS PEOPLES DAY — A PERSONAL LETTER FROM JESSICA CLEAR-WATER ARRIVES</t>
+          <t>WINTER HOLIDAYS AT THE WHITE HOUSE — THE LIGHTS ARE ON</t>
         </is>
       </c>
       <c r="C62" s="39" t="inlineStr">
         <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D62" s="40" t="inlineStr">
+        <is>
           <t>sensual</t>
         </is>
       </c>
-      <c r="D62" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>What Ualani Writes Back — and What She Does Not Put in the Letter but Means</t>
+          <t>The Night the President Spent Christmas Alone in the White House — and Was Not Quite Alone</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>nothing</t>
+          <t>morale_boost</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>WH_SECRET_10_BTN2</t>
+          <t>WH_SECRET_12_BTN2</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="38" t="inlineStr">
         <is>
-          <t>WH_SECRET_12</t>
+          <t>CA_PM_DOUBT</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>CHRISTMAS IN WASHINGTON — THE PRESIDENT IS FAR FROM HOME</t>
+          <t>PENOIT QUESTIONS THE MILITIA'S RESOLVE</t>
         </is>
       </c>
       <c r="C63" s="39" t="inlineStr">
         <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D63" s="40" t="inlineStr">
+        <is>
           <t>sensual</t>
         </is>
       </c>
-      <c r="D63" s="40" t="inlineStr">
-        <is>
-          <t>sensual</t>
-        </is>
-      </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>The Night the President Spent Christmas Alone in the White House — and Was Not Quite Alone</t>
+          <t>Penoit Needs More Than Words Right Now</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>WH_SECRET_12_BTN2</t>
+          <t>CA_PM_DOUBT_BTN2</t>
         </is>
       </c>
     </row>
